--- a/repair/back/doc/estimate/repair2.xlsx
+++ b/repair/back/doc/estimate/repair2.xlsx
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">㈜ 에 이 앤 비 </t>
   </si>
@@ -1178,6 +1178,9 @@
   </si>
   <si>
     <t>九</t>
+  </si>
+  <si>
+    <t>㈜에이앤비(이하 "수주자"라 한다)는 다음과 같이 계약을 체결한다.</t>
   </si>
 </sst>
 </file>
@@ -12853,7 +12856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -13654,6 +13657,45 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3167">
@@ -20683,7 +20725,7 @@
   <sheetPr>
     <tabColor rgb="92d050"/>
   </sheetPr>
-  <dimension ref="H1:AA116"/>
+  <dimension ref="H1:AA113"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="12.000000"/>
   <cols>
     <col min="1" max="7" style="1" width="11.29071413" customWidth="1" outlineLevel="0"/>
@@ -21846,13 +21888,13 @@
         <v>140</v>
       </c>
       <c r="N41" s="92"/>
-      <c r="O41" s="92" t="s">
+      <c r="O41" s="168" t="s">
         <v>137</v>
       </c>
-      <c r="P41" s="92"/>
-      <c r="Q41" s="92"/>
-      <c r="R41" s="92"/>
-      <c r="S41" s="92"/>
+      <c r="P41" s="168"/>
+      <c r="Q41" s="168"/>
+      <c r="R41" s="168"/>
+      <c r="S41" s="168"/>
       <c r="T41" s="92" t="s">
         <v>10</v>
       </c>
@@ -21860,13 +21902,13 @@
         <v>138</v>
       </c>
       <c r="V41" s="92"/>
-      <c r="W41" s="92" t="s">
+      <c r="W41" s="168" t="s">
         <v>139</v>
       </c>
-      <c r="X41" s="92"/>
-      <c r="Y41" s="92"/>
-      <c r="Z41" s="92"/>
-      <c r="AA41" s="135"/>
+      <c r="X41" s="168"/>
+      <c r="Y41" s="168"/>
+      <c r="Z41" s="168"/>
+      <c r="AA41" s="169"/>
     </row>
     <row r="42" spans="8:27" ht="24.950000" customHeight="1">
       <c r="H42" s="183"/>
@@ -22019,7 +22061,7 @@
       <c r="Z48" s="35"/>
       <c r="AA48" s="159"/>
     </row>
-    <row r="49" spans="7:27" ht="24.950000" customHeight="1">
+    <row r="49" spans="8:27" ht="24.950000" customHeight="1">
       <c r="H49" s="34"/>
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
@@ -22041,7 +22083,7 @@
       <c r="Z49" s="35"/>
       <c r="AA49" s="159"/>
     </row>
-    <row r="50" spans="7:27" ht="14.250000">
+    <row r="50" spans="8:27" ht="14.250000">
       <c r="H50" s="119"/>
       <c r="I50" s="120"/>
       <c r="J50" s="120"/>
@@ -22063,7 +22105,7 @@
       <c r="Z50" s="106"/>
       <c r="AA50" s="109"/>
     </row>
-    <row r="51" spans="7:27" ht="24.950000" customHeight="1">
+    <row r="51" spans="8:27" ht="24.950000" customHeight="1">
       <c r="H51" s="121" t="s">
         <v>170</v>
       </c>
@@ -22089,8 +22131,7 @@
       <c r="Z51" s="123"/>
       <c r="AA51" s="124"/>
     </row>
-    <row r="52" spans="7:27" ht="40.500000" customHeight="1">
-      <c r="G52" s="1"/>
+    <row r="52" spans="8:27" ht="40.500000" customHeight="1">
       <c r="H52" s="125" t="s">
         <v>93</v>
       </c>
@@ -22116,40 +22157,38 @@
       <c r="Z52" s="126"/>
       <c r="AA52" s="127"/>
     </row>
-    <row r="53" spans="7:27" ht="40.500000" customHeight="1">
-      <c r="G53" s="1"/>
+    <row r="53" spans="8:27" ht="40.500000" customHeight="1">
       <c r="H53" s="162" t="s">
         <v>95</v>
       </c>
       <c r="I53" s="259"/>
       <c r="J53" s="259"/>
-      <c r="K53" s="260" t="str">
+      <c r="K53" s="267" t="str">
         <f>M29</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="L53" s="260"/>
-      <c r="M53" s="260"/>
-      <c r="N53" s="260"/>
-      <c r="O53" s="260"/>
-      <c r="P53" s="260"/>
-      <c r="Q53" s="264"/>
+      <c r="L53" s="267"/>
+      <c r="M53" s="267"/>
+      <c r="N53" s="267"/>
+      <c r="O53" s="267"/>
+      <c r="P53" s="267"/>
+      <c r="Q53" s="268"/>
       <c r="R53" s="44" t="s">
         <v>96</v>
       </c>
       <c r="S53" s="44"/>
       <c r="T53" s="44"/>
-      <c r="U53" s="44" t="s">
+      <c r="U53" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="V53" s="44"/>
-      <c r="W53" s="44"/>
-      <c r="X53" s="44"/>
-      <c r="Y53" s="44"/>
-      <c r="Z53" s="44"/>
-      <c r="AA53" s="136"/>
-    </row>
-    <row r="54" spans="7:27" ht="40.500000" customHeight="1">
-      <c r="G54" s="1"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="35"/>
+      <c r="X53" s="35"/>
+      <c r="Y53" s="35"/>
+      <c r="Z53" s="35"/>
+      <c r="AA53" s="159"/>
+    </row>
+    <row r="54" spans="8:27" ht="40.500000" customHeight="1">
       <c r="H54" s="162" t="s">
         <v>98</v>
       </c>
@@ -22180,8 +22219,7 @@
       <c r="Z54" s="137"/>
       <c r="AA54" s="138"/>
     </row>
-    <row r="55" spans="7:27" ht="40.500000" customHeight="1">
-      <c r="G55" s="1"/>
+    <row r="55" spans="8:27" ht="40.500000" customHeight="1">
       <c r="H55" s="163" t="s">
         <v>174</v>
       </c>
@@ -22201,19 +22239,19 @@
       </c>
       <c r="S55" s="139"/>
       <c r="T55" s="139"/>
-      <c r="U55" s="139" t="s">
+      <c r="U55" s="269" t="s">
         <v>68</v>
       </c>
-      <c r="V55" s="139"/>
-      <c r="W55" s="139"/>
-      <c r="X55" s="139"/>
-      <c r="Y55" s="139"/>
-      <c r="Z55" s="139"/>
+      <c r="V55" s="269"/>
+      <c r="W55" s="269"/>
+      <c r="X55" s="269"/>
+      <c r="Y55" s="269"/>
+      <c r="Z55" s="269"/>
       <c r="AA55" s="112" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="7:27" ht="16.500000">
+    <row r="56" spans="8:27" ht="16.500000">
       <c r="H56" s="128" t="s">
         <v>63</v>
       </c>
@@ -22237,7 +22275,7 @@
       <c r="Z56" s="128"/>
       <c r="AA56" s="128"/>
     </row>
-    <row r="57" spans="7:27" ht="25.500000">
+    <row r="57" spans="8:27" ht="25.500000">
       <c r="H57" s="117" t="s">
         <v>91</v>
       </c>
@@ -22261,71 +22299,71 @@
       <c r="Z57" s="117"/>
       <c r="AA57" s="117"/>
     </row>
-    <row r="58" spans="7:27" ht="14.250000">
+    <row r="58" spans="8:27" ht="14.250000">
       <c r="H58" s="26"/>
       <c r="L58" s="29"/>
       <c r="M58" s="30"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="7:27" ht="20.000000" customHeight="1">
-      <c r="H59" s="35" t="s">
+    <row r="59" spans="8:27" ht="20.000000" customHeight="1">
+      <c r="H59" s="270"/>
+      <c r="I59" s="277" t="s">
         <v>167</v>
       </c>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="35"/>
-      <c r="O59" s="35"/>
-      <c r="P59" s="35"/>
-      <c r="Q59" s="35"/>
-      <c r="R59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="T59" s="35"/>
-      <c r="U59" s="35"/>
-      <c r="V59" s="35"/>
-      <c r="W59" s="35"/>
-      <c r="X59" s="35"/>
-      <c r="Y59" s="35"/>
-      <c r="Z59" s="35"/>
-      <c r="AA59" s="35"/>
-    </row>
-    <row r="60" spans="7:27" ht="20.000000" customHeight="1">
-      <c r="H60" s="35" t="s">
+      <c r="J59" s="277"/>
+      <c r="K59" s="277"/>
+      <c r="L59" s="277"/>
+      <c r="M59" s="277"/>
+      <c r="N59" s="277"/>
+      <c r="O59" s="277"/>
+      <c r="P59" s="277"/>
+      <c r="Q59" s="277"/>
+      <c r="R59" s="277"/>
+      <c r="S59" s="277"/>
+      <c r="T59" s="277"/>
+      <c r="U59" s="277"/>
+      <c r="V59" s="277"/>
+      <c r="W59" s="277"/>
+      <c r="X59" s="277"/>
+      <c r="Y59" s="277"/>
+      <c r="Z59" s="277"/>
+      <c r="AA59" s="277"/>
+    </row>
+    <row r="60" spans="8:27" ht="20.000000" customHeight="1">
+      <c r="H60" s="270"/>
+      <c r="I60" s="277" t="s">
         <v>168</v>
       </c>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-    </row>
-    <row r="61" spans="7:27" ht="20.000000" customHeight="1">
-      <c r="H61" s="118" t="str">
+      <c r="J60" s="277"/>
+      <c r="K60" s="277"/>
+      <c r="L60" s="277"/>
+      <c r="M60" s="277"/>
+      <c r="N60" s="277"/>
+      <c r="O60" s="277"/>
+      <c r="P60" s="277"/>
+      <c r="Q60" s="277"/>
+      <c r="R60" s="277"/>
+      <c r="S60" s="277"/>
+      <c r="T60" s="277"/>
+      <c r="U60" s="277"/>
+      <c r="V60" s="277"/>
+      <c r="W60" s="277"/>
+      <c r="X60" s="277"/>
+      <c r="Y60" s="277"/>
+      <c r="Z60" s="277"/>
+      <c r="AA60" s="277"/>
+    </row>
+    <row r="61" spans="8:27" ht="20.000000" customHeight="1">
+      <c r="H61" s="273"/>
+      <c r="I61" s="278" t="str">
         <f>K53</f>
         <v>마곡엠밸리4단지아파트</v>
       </c>
-      <c r="I61" s="118"/>
-      <c r="J61" s="118"/>
-      <c r="K61" s="118"/>
-      <c r="L61" s="118"/>
-      <c r="M61" s="118"/>
-      <c r="N61" s="118"/>
+      <c r="J61" s="278"/>
+      <c r="K61" s="278"/>
+      <c r="L61" s="278"/>
+      <c r="M61" s="278"/>
+      <c r="N61" s="278"/>
       <c r="O61" s="36" t="s">
         <v>172</v>
       </c>
@@ -22342,31 +22380,31 @@
       <c r="Z61" s="36"/>
       <c r="AA61" s="36"/>
     </row>
-    <row r="62" spans="7:27" ht="20.000000" customHeight="1">
-      <c r="H62" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="I62" s="36"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="36"/>
-      <c r="L62" s="36"/>
-      <c r="M62" s="36"/>
-      <c r="N62" s="36"/>
-      <c r="O62" s="36"/>
-      <c r="P62" s="36"/>
-      <c r="Q62" s="36"/>
-      <c r="R62" s="36"/>
-      <c r="S62" s="36"/>
-      <c r="T62" s="36"/>
-      <c r="U62" s="36"/>
-      <c r="V62" s="36"/>
-      <c r="W62" s="36"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="36"/>
-      <c r="Z62" s="36"/>
-      <c r="AA62" s="36"/>
-    </row>
-    <row r="63" spans="7:27" ht="20.000000" customHeight="1">
+    <row r="62" spans="8:27" ht="20.000000" customHeight="1">
+      <c r="H62" s="275"/>
+      <c r="I62" s="279" t="s">
+        <v>192</v>
+      </c>
+      <c r="J62" s="279"/>
+      <c r="K62" s="279"/>
+      <c r="L62" s="279"/>
+      <c r="M62" s="279"/>
+      <c r="N62" s="279"/>
+      <c r="O62" s="279"/>
+      <c r="P62" s="279"/>
+      <c r="Q62" s="279"/>
+      <c r="R62" s="279"/>
+      <c r="S62" s="279"/>
+      <c r="T62" s="279"/>
+      <c r="U62" s="279"/>
+      <c r="V62" s="279"/>
+      <c r="W62" s="279"/>
+      <c r="X62" s="279"/>
+      <c r="Y62" s="279"/>
+      <c r="Z62" s="279"/>
+      <c r="AA62" s="279"/>
+    </row>
+    <row r="63" spans="8:27" ht="20.000000" customHeight="1">
       <c r="H63" s="35"/>
       <c r="I63" s="35"/>
       <c r="J63" s="35"/>
@@ -22377,7 +22415,7 @@
       <c r="O63" s="35"/>
       <c r="P63" s="35"/>
     </row>
-    <row r="64" spans="7:27" ht="20.000000" customHeight="1">
+    <row r="64" spans="8:27" ht="20.000000" customHeight="1">
       <c r="H64" s="114" t="s">
         <v>149</v>
       </c>
@@ -23431,11 +23469,11 @@
     <mergeCell ref="U55:Z55"/>
     <mergeCell ref="H56:AA56"/>
     <mergeCell ref="H57:AA57"/>
-    <mergeCell ref="H59:AA59"/>
-    <mergeCell ref="H60:AA60"/>
-    <mergeCell ref="H61:N61"/>
+    <mergeCell ref="I59:AA59"/>
+    <mergeCell ref="I60:AA60"/>
+    <mergeCell ref="I61:N61"/>
     <mergeCell ref="O61:AA61"/>
-    <mergeCell ref="H62:AA62"/>
+    <mergeCell ref="I62:AA62"/>
     <mergeCell ref="H64:P64"/>
     <mergeCell ref="I65:AA65"/>
     <mergeCell ref="H67:AA67"/>
